--- a/data/trans_orig/IP07_A11_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07_A11_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el adulto en 2023 (tasa de respuesta: 99,9%)</t>
+          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el/la adulto/a en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6079</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11748</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3232</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>791</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7838</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>16618</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>593</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4368</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10673</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10373</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23415</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16335</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31894</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,52%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6322</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3210</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11583</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24062</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33901</t>
+          <t>12601</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30384</t>
+          <t>30014</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21738</t>
+          <t>21474</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41319</t>
+          <t>39769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>125192</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>115248</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>134476</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>77,64%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>113707</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>106170</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>119405</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,37%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,52%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>134618</t>
+          <t>113124</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124017</t>
+          <t>105717</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>144519</t>
+          <t>118939</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>248325</t>
+          <t>238315</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>235193</t>
+          <t>226741</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>259151</t>
+          <t>250005</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,61%</t>
         </is>
       </c>
     </row>
@@ -1285,74 +1285,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>161237</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>161237</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>161237</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>130472</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>130472</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>130472</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>130801</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>130801</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>130801</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>171327</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>171327</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>171327</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>371</t>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>301799</t>
+          <t>292037</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>301799</t>
+          <t>292037</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>301799</t>
+          <t>292037</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17348</t>
+          <t>17981</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11474</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t>27346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5920</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3337</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7918</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6611</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32337</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5806</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2432</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12293</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,22 +1703,22 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>23788</t>
+          <t>19536</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>11894</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43772</t>
+          <t>37434</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20923</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13652</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30698</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16407</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9617</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24535</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20082</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13699</t>
+          <t>11176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>26124</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>36489</t>
+          <t>38636</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26499</t>
+          <t>29459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49455</t>
+          <t>51536</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>213077</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>195588</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>224489</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75,59%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>205073</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>194403</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>216934</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>85,92%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>219314</t>
+          <t>188705</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197737</t>
+          <t>178566</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>232307</t>
+          <t>197849</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>424386</t>
+          <t>401782</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>402504</t>
+          <t>382450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>444261</t>
+          <t>416828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -1967,74 +1967,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>258747</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>258747</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>258747</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>299</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>238680</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>238680</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>238680</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>224653</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>224653</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>224653</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>268398</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>268398</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>268398</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>593</t>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>507077</t>
+          <t>483400</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>507077</t>
+          <t>483400</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>507077</t>
+          <t>483400</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15497</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9591</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25579</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>11289</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5896</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18260</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37984</t>
+          <t>39966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4187</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9035</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>5549</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>10229</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17478</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>17694</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9440</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>31362</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>10806</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6363</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17662</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47243</t>
+          <t>19440</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57408</t>
+          <t>45246</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>44337</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>33724</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>58156</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>22728</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>15577</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>32350</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33080</t>
+          <t>16402</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58709</t>
+          <t>33975</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>66873</t>
+          <t>68650</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52815</t>
+          <t>54405</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81402</t>
+          <t>82889</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>338269</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>320413</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>352690</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>80,54%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>76,29%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>83,98%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>406</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>318780</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>306785</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>332663</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>86,35%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>353931</t>
+          <t>301828</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332203</t>
+          <t>288634</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>370907</t>
+          <t>313203</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>672711</t>
+          <t>640096</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>647219</t>
+          <t>619358</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>695108</t>
+          <t>660123</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -2649,74 +2649,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>355453</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>355453</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>355453</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>439724</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>439724</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>439724</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>964</t>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
